--- a/Products.xlsx
+++ b/Products.xlsx
@@ -1,62 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bagallery-importor\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C257B-BAC8-4A5C-95D1-10785ED98EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Fragrances</t>
-  </si>
-  <si>
-    <t>Lattafa</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <charset val="178"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="178"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -75,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -389,35 +420,127 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="75.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col width="75.21875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="6.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lattafa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Uploaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml-1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lattafa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Uploaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://bagallery.com/collections/lattafa/products/asad-men-edp-100ml</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lattafa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Uploaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://bagallery.com/collections/lattafa/products/lattafa-yara-edp-100ml</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lattafa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Uploaded</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Products.xlsx
+++ b/Products.xlsx
@@ -1,34 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\banaat-darse-nizaami\shopify-importer\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC90CCBB-5D17-4B15-9C1E-7111881DEEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
+  </si>
+  <si>
+    <t>Fragrances</t>
+  </si>
+  <si>
+    <t>Lattafa</t>
+  </si>
+  <si>
+    <t>Uploaded</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml-1</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/asad-men-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-yara-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-his-confession-men-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-dukhan-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/ejaazi-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-angham-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-men-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-lattafa-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/al-dur-al-maknoon-edp-100ml</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="178"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +117,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,127 +431,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="75.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="9.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="6.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="75.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fragrances</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lattafa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Uploaded</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml-1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Fragrances</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Lattafa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Uploaded</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://bagallery.com/collections/lattafa/products/asad-men-edp-100ml</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fragrances</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lattafa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Uploaded</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://bagallery.com/collections/lattafa/products/lattafa-yara-edp-100ml</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fragrances</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Lattafa</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Uploaded</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Products.xlsx
+++ b/Products.xlsx
@@ -1,104 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\banaat-darse-nizaami\shopify-importer\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC90CCBB-5D17-4B15-9C1E-7111881DEEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
-  </si>
-  <si>
-    <t>Fragrances</t>
-  </si>
-  <si>
-    <t>Lattafa</t>
-  </si>
-  <si>
-    <t>Uploaded</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml-1</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/asad-men-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-yara-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-his-confession-men-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-dukhan-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/ejaazi-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-angham-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-men-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-lattafa-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/al-dur-al-maknoon-edp-100ml</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <charset val="178"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="178"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -117,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -431,101 +420,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="75.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col width="75.21875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>19</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Uploaded</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Products.xlsx
+++ b/Products.xlsx
@@ -1,34 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\banaat-darse-nizaami\shopify-importer\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C5D528-1C49-4D12-9E1B-3E11B2A00F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Fragrances</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml-1</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/asad-men-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-yara-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-his-confession-men-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-dukhan-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/ejaazi-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-angham-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-men-edp-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-lattafa-100ml</t>
+  </si>
+  <si>
+    <t>https://bagallery.com/collections/lattafa/products/al-dur-al-maknoon-edp-100ml</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="178"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +108,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,50 +422,127 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="75.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="9.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="75.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fragrances</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Uploaded</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Products.xlsx
+++ b/Products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\banaat-darse-nizaami\shopify-importer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C5D528-1C49-4D12-9E1B-3E11B2A00F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5A63C7-8BA9-441C-825D-2E56B9FB3619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>URL</t>
   </si>
@@ -28,59 +28,32 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Brand</t>
   </si>
   <si>
-    <t>Fragrances</t>
+    <t>Product Description</t>
   </si>
   <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-opulent-dubai-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml-1</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/asad-men-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-yara-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-his-confession-men-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-dukhan-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/ejaazi-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-khamrah-qahwa-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-angham-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-men-edp-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/lattafa-fakhar-lattafa-100ml</t>
-  </si>
-  <si>
-    <t>https://bagallery.com/collections/lattafa/products/al-dur-al-maknoon-edp-100ml</t>
+    <t>Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
@@ -104,13 +77,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -423,14 +399,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="75.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="81.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" customWidth="1"/>
+    <col min="4" max="4" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,110 +418,15 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Products.xlsx
+++ b/Products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\banaat-darse-nizaami\shopify-importer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5A63C7-8BA9-441C-825D-2E56B9FB3619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE69739-B237-44A9-888F-1EEBE792E807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Products.xlsx
+++ b/Products.xlsx
@@ -1,68 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\banaat-darse-nizaami\shopify-importer\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE69739-B237-44A9-888F-1EEBE792E807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Product Description</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <charset val="178"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="178"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="Calibri"/>
+      <charset val="178"/>
+      <family val="2"/>
+      <color theme="10"/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="178"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,23 +57,82 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -398,35 +432,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="81.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" customWidth="1"/>
-    <col min="4" max="4" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col width="165.21875" customWidth="1" min="1" max="1"/>
+    <col width="13.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13.5546875" customWidth="1" min="3" max="3"/>
+    <col width="9.77734375" customWidth="1" min="4" max="4"/>
+    <col width="27.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://bagallery.com/collections/beauty-false-eye-lashes/products/shein-sheglam-lash-pages-multi-style-hybrid-lash-clusters</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Testt</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Uploaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
